--- a/hall/resources/sample/PassReward.xlsx
+++ b/hall/resources/sample/PassReward.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="79">
   <si>
     <t>序号ID</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
     <t>map&lt;int{_}long&gt;{|}</t>
@@ -1477,39 +1474,39 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="17.25" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:7">
@@ -1535,13 +1532,13 @@
         <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:7">
@@ -1559,13 +1556,13 @@
         <v>80</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:7">
@@ -1583,13 +1580,13 @@
         <v>120</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:7">
@@ -1607,13 +1604,13 @@
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:7">
@@ -1631,13 +1628,13 @@
         <v>200</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:7">
@@ -1655,13 +1652,13 @@
         <v>240</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:7">
@@ -1679,13 +1676,13 @@
         <v>280</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:7">
@@ -1703,13 +1700,13 @@
         <v>320</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
@@ -1727,13 +1724,13 @@
         <v>360</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
@@ -1751,13 +1748,13 @@
         <v>400</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
@@ -1775,13 +1772,13 @@
         <v>440</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
@@ -1799,13 +1796,13 @@
         <v>480</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
@@ -1823,13 +1820,13 @@
         <v>520</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:7">
@@ -1847,13 +1844,13 @@
         <v>560</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:7">
@@ -1871,13 +1868,13 @@
         <v>600</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:7">
@@ -1895,13 +1892,13 @@
         <v>640</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:7">
@@ -1919,13 +1916,13 @@
         <v>680</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:7">
@@ -1943,13 +1940,13 @@
         <v>720</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:7">
@@ -1967,13 +1964,13 @@
         <v>760</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:7">
@@ -1991,13 +1988,13 @@
         <v>800</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:7">
@@ -2015,13 +2012,13 @@
         <v>840</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:7">
@@ -2039,13 +2036,13 @@
         <v>880</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:7">
@@ -2063,13 +2060,13 @@
         <v>920</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:7">
@@ -2087,13 +2084,13 @@
         <v>960</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:7">
@@ -2111,13 +2108,13 @@
         <v>1000</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:7">
@@ -2135,13 +2132,13 @@
         <v>1040</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:7">
@@ -2159,13 +2156,13 @@
         <v>1080</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:7">
@@ -2183,13 +2180,13 @@
         <v>1120</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:7">
@@ -2207,13 +2204,13 @@
         <v>1160</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:7">
@@ -2231,13 +2228,13 @@
         <v>1200</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="G34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:7">
@@ -2255,13 +2252,13 @@
         <v>1240</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:7">
@@ -2279,13 +2276,13 @@
         <v>1280</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:7">
@@ -2303,13 +2300,13 @@
         <v>1320</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:7">
@@ -2327,13 +2324,13 @@
         <v>1360</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:7">
@@ -2351,13 +2348,13 @@
         <v>1400</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:7">
@@ -2375,13 +2372,13 @@
         <v>1440</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:7">
@@ -2399,13 +2396,13 @@
         <v>1480</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:7">
@@ -2423,13 +2420,13 @@
         <v>1520</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:7">
@@ -2447,13 +2444,13 @@
         <v>1560</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:7">
@@ -2471,13 +2468,13 @@
         <v>1600</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:7">
@@ -2495,13 +2492,13 @@
         <v>1640</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:7">
@@ -2519,13 +2516,13 @@
         <v>1680</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:7">
@@ -2543,13 +2540,13 @@
         <v>1720</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:7">
@@ -2567,13 +2564,13 @@
         <v>1760</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:7">
@@ -2591,13 +2588,13 @@
         <v>1800</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:7">
@@ -2615,13 +2612,13 @@
         <v>1840</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:7">
@@ -2639,13 +2636,13 @@
         <v>1880</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:7">
@@ -2663,13 +2660,13 @@
         <v>1920</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:7">
@@ -2687,13 +2684,13 @@
         <v>1960</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:7">
@@ -2711,13 +2708,13 @@
         <v>2000</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
